--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0213.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0213.xlsx
@@ -8504,7 +8504,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>[Lời Cuối Cùng] Ta muốn những trận chiến khốc liệt hơn.</t>
+          <t>[Lời Cuối Cùng] Tao muốn những trận chiến khốc liệt hơn.</t>
         </is>
       </c>
     </row>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>[Lời Cuối Cùng] Ta đang đợi một người đặc biệt.</t>
+          <t>[Lời Cuối Cùng] Tao đang đợi một người đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Activated Synergy Burst: {0}&lt;/color&gt;</t>
+          <t>&lt;color=Highlight&gt;Kích Hoạt Đồng Bộ Bùng Nổ: {0}&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Làm Mới ({0}/{1})</t>
+          <t>Làm mới ({0}/{1})</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>&lt;color=#fb8d0a&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Feilian Beringal &lt;color=#b72924ff&gt;pulls in&lt;/color&gt; các Cộng Hưởng Giả về phía mình mỗi &lt;color=#b72924ff&gt;10s&lt;/color&gt;.</t>
+          <t>Feilian Beringal &lt;color=#b72924ff&gt;kéo&lt;/color&gt; các Resonator về phía mình mỗi &lt;color=#b72924ff&gt;10 giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Feilian Beringal &lt;color=#b72924ff&gt;knocks back&lt;/color&gt; các Cộng Hưởng Giả xung quanh mỗi &lt;color=#b72924ff&gt;10 giây&lt;/color&gt;.</t>
+          <t>Feilian Beringal &lt;color=#b72924ff&gt;hất văng&lt;/color&gt; các Resonator xung quanh mỗi &lt;color=#b72924ff&gt;10 giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11039,7 +11039,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Queen of the Night được &lt;color=#b72924ff&gt;empowered&lt;/color&gt;.</t>
+          <t>Queen of the Night được &lt;color=#b72924ff&gt;tăng cường mạnh mẽ&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả &lt;color=#b72924ff&gt;receive 20% less Healing&lt;/color&gt;.</t>
+          <t>Resonator &lt;color=#b72924ff&gt;chỉ nhận được 80% lượng hồi phục&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11169,7 +11169,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả &lt;color=#b72924ff&gt;receive 40% less Healing&lt;/color&gt;.</t>
+          <t>Resonator &lt;color=#b72924ff&gt;chỉ nhận được 60% lượng hồi phục&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>&lt;color=#b72924ff&gt;Symphony Rank efficiency is reduced by 25%&lt;/color&gt;.</t>
+          <t>&lt;color=#b72924ff&gt;Hiệu suất Cấp Độ Giao Hưởng giảm 25%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>&lt;color=#b72924ff&gt;Symphony Rank efficiency is reduced by 50%&lt;/color&gt;.</t>
+          <t>&lt;color=#b72924ff&gt;Hiệu suất Cấp Độ Giao Hưởng giảm 50%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Thẩm phán đặc biệt {0} đã tham dự buổi chiếu giới hạn "Biến Đổiing Hero: Flame Ranger" vào ngày {1} tại Rạp 1. Đây là bản ghi chi tiết:</t>
+          <t>Thẩm phán đặc biệt {0} đã tham dự buổi chiếu giới hạn "Transforming Hero: Flame Ranger" vào ngày {1} tại Rạp 1. Đây là bản ghi chi tiết:</t>
         </is>
       </c>
     </row>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Tin buồn: Thẩm phán đặc biệt {0} đã bị mắc kẹt trong giấc mơ vào ngày {1}, khi đang tham dự buổi chiếu giới hạn phim "Biến Đổiing Hero: Flame Ranger" tại Rạp 1.</t>
+          <t>Tin buồn: Thẩm phán đặc biệt {0} đã bị mắc kẹt trong giấc mơ vào ngày {1}, khi đang tham dự buổi chiếu giới hạn phim "Transforming Hero: Flame Ranger" tại Rạp 1.</t>
         </is>
       </c>
     </row>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Tốc độ phục hồi Năng Lượng của Cộng Hưởng Giả tăng 100%.</t>
+          <t>Tốc độ phục hồi Năng Lượng của Resonator tăng 100%.</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả nhận thêm 40% Hiệu Quả Hồi Phục.</t>
+          <t>Resonator nhận thêm 40% Hiệu Quả Hồi Phục.</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Feilian Beringal triệu hồi và tăng cường sức mạnh cho &lt;color=#b72924ff&gt;Havoc Dreadmane, Spearback, and Hoochief Menace&lt;/color&gt;.</t>
+          <t>Feilian Beringal triệu hồi và tăng cường sức mạnh cho &lt;color=#b72924ff&gt;Havoc Dreadmane, Spearback và Hoochief Menace&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Cấp độ trung bình của Cộng Hưởng Giả hiện tại thấp hơn mức khuyến nghị. Bạn có muốn tiếp tục không?</t>
+          <t>Cấp độ trung bình của Resonator hiện tại thấp hơn mức khuyến nghị. Bạn có muốn tiếp tục không?</t>
         </is>
       </c>
     </row>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Bong bóng hồi phục tăng &lt;color=#b72924ff&gt;150% more Healing&lt;/color&gt;.</t>
+          <t>Bong bóng hồi phục tăng &lt;color=#b72924ff&gt;150% hiệu ứng chữa trị&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Fleurdelys đã được &lt;color=#b72924ff&gt;empowered&lt;/color&gt; mạnh mẽ.</t>
+          <t>Fleurdelys đã được &lt;color=#b72924ff&gt;tiếp sức&lt;/color&gt; mạnh mẽ.</t>
         </is>
       </c>
     </row>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Feilian Beringal được &lt;color=#b72924ff&gt;empowered&lt;/color&gt; đáng kể.</t>
+          <t>Feilian Beringal được &lt;color=#b72924ff&gt;tăng cường sức mạnh&lt;/color&gt; đáng kể.</t>
         </is>
       </c>
     </row>
@@ -13639,7 +13639,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Ảo Tưởng Vô Hồi giờ đây &lt;color=#b72924ff&gt;empowered&lt;/color&gt; mạnh mẽ.</t>
+          <t>Ảo Tưởng Vô Hồi giờ đây &lt;color=#b72924ff&gt;được tăng cường&lt;/color&gt; mạnh mẽ.</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Hoàn thành Tiếng Vang Bão Kiếm với Mô-đun Áp Lực: Giòn và Pháo Đài Tuyệt Vọng: Khiên được trang bị</t>
+          <t>Hoàn thành Echo Bão Kiếm với Mô-đun Áp Lực: Giòn và Pháo Đài Tuyệt Vọng: Khiên được trang bị</t>
         </is>
       </c>
     </row>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Thưởng từ Vương Quốc Giáo và Vương Quốc Khiên &lt;color=#b72924ff&gt;are 50% weaker&lt;/color&gt;.</t>
+          <t>Thưởng từ Vương Quốc Giáo và Vương Quốc Khiên &lt;color=#b72924ff&gt;giảm 50%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Không đủ Cộng Hưởng Giả còn sống trong đội. Không thể kích hoạt Đồng Tâm Cực Khả.</t>
+          <t>Không đủ Resonator còn sống trong đội. Không thể kích hoạt Đồng Tâm Cực Khả.</t>
         </is>
       </c>
     </row>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Nhận thêm 1 lần &lt;te href=851012&gt;&lt;color=#c79f49&gt;Echo Recruitment&lt;/color&gt;&lt;/te&gt; trong ngày đầu tiên.</t>
+          <t>Nhận thêm 1 lần &lt;te href=851012&gt;&lt;color=#c79f49&gt;Tuyển Mộ Cộng Hưởng&lt;/color&gt;&lt;/te&gt; trong ngày đầu tiên.</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Bắt đầu với thêm 5 &lt;te href=851011&gt;&lt;color=#c79f49&gt;Frequency Crystals&lt;/color&gt;&lt;/te&gt; nữa.</t>
+          <t>Bắt đầu với thêm 5 &lt;te href=851011&gt;&lt;color=#c79f49&gt;Tinh thể Tần số&lt;/color&gt;&lt;/te&gt; nữa.</t>
         </is>
       </c>
     </row>
@@ -14354,7 +14354,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Một Echo hạng xanh lam chắc chắn sẽ xuất hiện trong &lt;te href=851012&gt;&lt;color=#c79f49&gt;Echo Recruitment&lt;/color&gt;&lt;/te&gt; vào ngày đầu tiên.</t>
+          <t>Một Echo hạng xanh lam chắc chắn sẽ xuất hiện trong &lt;te href=851012&gt;&lt;color=#c79f49&gt;Tuyển Dụng Echo&lt;/color&gt;&lt;/te&gt; vào ngày đầu tiên.</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Nhận thêm 1 lần làm mới miễn phí &lt;te href=851012&gt;&lt;color=#c79f49&gt;Echo Recruitment&lt;/color&gt;&lt;/te&gt; mỗi Giai Đoạn. Số lần không dùng có thể chuyển sang Giai Đoạn tiếp theo.</t>
+          <t>Nhận thêm 1 lần làm mới miễn phí &lt;te href=851012&gt;&lt;color=#c79f49&gt;Tuyển Mộ Cộng Hưởng&lt;/color&gt;&lt;/te&gt; mỗi Giai Đoạn. Số lần không dùng có thể chuyển sang Giai Đoạn tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -14614,7 +14614,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Nhận thêm 2 &lt;te href=851011&gt;&lt;color=#c79f49&gt;Frequency Crystals&lt;/color&gt;&lt;/te&gt; vào cuối mỗi Giai Đoạn.</t>
+          <t>Nhận thêm 2 &lt;te href=851011&gt;&lt;color=#c79f49&gt;Tinh Thể Tần Số&lt;/color&gt;&lt;/te&gt; vào cuối mỗi Giai Đoạn.</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Sau khi vào Chế Độ Vô Tận, mỗi ngày bạn sẽ nhận được thêm số &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Coupons&lt;/color&gt;&lt;/te&gt; bằng 5% Sản Lượng Hôm Nay.</t>
+          <t>Sau khi vào Chế Độ Vô Tận, mỗi ngày bạn sẽ nhận được thêm số &lt;te href=851010&gt;&lt;color=#c79f49&gt;Phiếu Mộng Ảnh&lt;/color&gt;&lt;/te&gt; bằng 5% Sản Lượng Hôm Nay.</t>
         </is>
       </c>
     </row>
@@ -14939,7 +14939,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Bắt đầu với thêm 5 &lt;te href=851011&gt;&lt;color=#c79f49&gt;Frequency Crystals&lt;/color&gt;&lt;/te&gt; nữa.</t>
+          <t>Bắt đầu với thêm 5 &lt;te href=851011&gt;&lt;color=#c79f49&gt;Tinh thể Tần số&lt;/color&gt;&lt;/te&gt; nữa.</t>
         </is>
       </c>
     </row>
@@ -15004,7 +15004,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Nhận thêm 2 &lt;te href=851011&gt;&lt;color=#c79f49&gt;Frequency Crystals&lt;/color&gt;&lt;/te&gt; vào cuối mỗi Giai Đoạn.</t>
+          <t>Nhận thêm 2 &lt;te href=851011&gt;&lt;color=#c79f49&gt;Tinh Thể Tần Số&lt;/color&gt;&lt;/te&gt; vào cuối mỗi Giai Đoạn.</t>
         </is>
       </c>
     </row>
@@ -15719,7 +15719,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Sau khi vào Chế Độ Vô Tận, mỗi ngày bạn sẽ nhận được thêm số &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Coupons&lt;/color&gt;&lt;/te&gt; bằng 5% Sản Lượng Hôm Nay.</t>
+          <t>Sau khi vào Chế Độ Vô Tận, mỗi ngày bạn sẽ nhận được thêm số &lt;te href=851010&gt;&lt;color=#c79f49&gt;Phiếu Mộng Ảnh&lt;/color&gt;&lt;/te&gt; bằng 5% Sản Lượng Hôm Nay.</t>
         </is>
       </c>
     </row>
@@ -17669,7 +17669,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Tin hay không thì tùy, ta từng có một chiếc thuyền nhanh y chang thế này. Một con thuyền đẹp tuyệt vời, trang bị toàn đồ câu xịn... *thở dài*.</t>
+          <t>Tin hay không thì tùy, tao từng có một chiếc thuyền nhanh y chang thế này. Một con thuyền đẹp tuyệt vời, trang bị toàn đồ câu xịn... *thở dài*.</t>
         </is>
       </c>
     </row>
@@ -18254,7 +18254,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Ha! Muốn trổ tài à? Ta đi cùng!</t>
+          <t>Ha! Muốn trổ tài à? Tao đi cùng!</t>
         </is>
       </c>
     </row>
@@ -21179,7 +21179,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>&lt;color=#b09a66ff&gt;{0}&lt;/color&gt;/&lt;color=#99929cff&gt;{1}&lt;/color&gt;</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -22934,7 +22934,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Mẹo của Namipon: Trang bị Sticker độc quyền cho Cộng Hưởng Giả sẽ tăng cường đáng kể sức chiến đấu của họ.</t>
+          <t>Mẹo của Namipon: Equipping a Resonator with their exclusive Sticker can greatly enhance their combat performance.</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>&lt;color=#efece1&gt;Common&lt;/color&gt;, &lt;color=#59b4d3&gt;Rare&lt;/color&gt;</t>
+          <t>&lt;color=#efece1&gt;Thường&lt;/color&gt;, &lt;color=#59b4d3&gt;Hiếm&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -24039,7 +24039,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>&lt;color=#59b4d3&gt;Rare&lt;/color&gt;, &lt;color=#ca6dff&gt;Unique&lt;/color&gt;</t>
+          <t>&lt;color=#59b4d3&gt;Hiếm&lt;/color&gt;, &lt;color=#ca6dff&gt;Độc Nhất&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -24104,7 +24104,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>&lt;color=#ca6dff&gt;Unique&lt;/color&gt;, &lt;color=#ffe65a&gt;Limited&lt;/color&gt;</t>
+          <t>&lt;color=#ca6dff&gt;Độc Nhất&lt;/color&gt;, &lt;color=#ffe65a&gt;Giới Hạn&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -24299,7 +24299,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>&lt;color=#ed354d&gt;Legendary&lt;/color&gt;</t>
+          <t>&lt;color=#ed354d&gt;Huyền Thoại&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -24494,7 +24494,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>&lt;color=#c15a55ff&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -26704,7 +26704,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Dù có ai nhìn thấy hay nghe thấy nữa thì cũng chẳng quan trọng! Ta phải trở thành một Cộng Hưởng Giả chân chính…</t>
+          <t>Dù có ai nhìn thấy hay nghe thấy nữa thì cũng chẳng quan trọng! Ta phải trở thành một Resonator chân chính…</t>
         </is>
       </c>
     </row>
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Nghe ta nói không?! Meo meo meo!</t>
+          <t>Nghe tao nói không?! Meo meo meo!</t>
         </is>
       </c>
     </row>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Cánh cổng đưa bạn đến &lt;color=#efece1&gt;Honami Central Park&lt;/color&gt;.</t>
+          <t>Cánh cổng đưa bạn đến &lt;color=#efece1&gt;Công viên Trung tâm Honami&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28134,7 +28134,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Cánh cổng đưa bạn trở về &lt;color=#efece1&gt;Central Honami&lt;/color&gt;.</t>
+          <t>Cánh cổng đưa bạn trở về &lt;color=#efece1&gt;Honami Trung tâm&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
